--- a/data/trans_camb/IP04D$notiene-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 14,69</t>
+          <t>3,46; 14,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 21,6</t>
+          <t>5,52; 22,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 16,67</t>
+          <t>4,16; 16,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 9,37</t>
+          <t>-2,44; 9,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,81</t>
+          <t>5,38; 13,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 14,1</t>
+          <t>3,18; 14,25</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,9; 583,26</t>
+          <t>34,31; 517,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,96; 746,83</t>
+          <t>56,55; 734,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,0; 705,81</t>
+          <t>56,07; 652,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 365,79</t>
+          <t>-48,91; 404,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,98; 432,04</t>
+          <t>78,14; 427,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,45; 427,77</t>
+          <t>52,34; 427,29</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,97</t>
+          <t>4,29; 12,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 16,99</t>
+          <t>6,11; 16,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,58</t>
+          <t>7,27; 14,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 12,94</t>
+          <t>3,36; 12,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,68</t>
+          <t>6,77; 12,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,4</t>
+          <t>5,68; 12,86</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,21; 642,83</t>
+          <t>81,67; 587,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>121,74; 825,45</t>
+          <t>125,34; 799,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138,3; 692,92</t>
+          <t>138,19; 701,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,75; 538,91</t>
+          <t>64,56; 548,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>140,55; 484,05</t>
+          <t>139,58; 493,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>128,46; 478,63</t>
+          <t>123,42; 488,31</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 15,31</t>
+          <t>5,63; 14,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,42</t>
+          <t>3,18; 12,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 17,38</t>
+          <t>6,81; 17,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 20,45</t>
+          <t>7,34; 20,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 14,65</t>
+          <t>7,39; 14,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,37</t>
+          <t>7,07; 15,2</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97,61; 969,26</t>
+          <t>88,93; 862,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,13; 815,55</t>
+          <t>46,37; 716,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,69; 592,63</t>
+          <t>83,5; 673,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91,78; 717,92</t>
+          <t>87,54; 615,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>116,1; 540,32</t>
+          <t>124,43; 541,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114,62; 538,9</t>
+          <t>115,95; 576,16</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 14,38</t>
+          <t>3,64; 13,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 15,44</t>
+          <t>2,93; 15,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 15,79</t>
+          <t>5,54; 15,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 16,38</t>
+          <t>5,51; 16,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 13,55</t>
+          <t>6,32; 13,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 14,0</t>
+          <t>5,49; 14,26</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>45,88; 423,75</t>
+          <t>38,71; 413,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32,9; 449,67</t>
+          <t>31,38; 450,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,61; 667,91</t>
+          <t>82,63; 729,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70,37; 733,2</t>
+          <t>94,0; 804,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>97,38; 413,42</t>
+          <t>106,44; 424,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,01; 451,32</t>
+          <t>91,93; 442,59</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,42</t>
+          <t>6,86; 11,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,17</t>
+          <t>6,66; 13,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,77</t>
+          <t>8,7; 13,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,23</t>
+          <t>6,92; 13,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,79</t>
+          <t>8,29; 11,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,07</t>
+          <t>7,46; 12,17</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>134,44; 351,49</t>
+          <t>131,52; 356,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>125,54; 385,4</t>
+          <t>133,5; 387,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168,12; 436,14</t>
+          <t>168,1; 440,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135,48; 402,23</t>
+          <t>135,43; 396,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>173,21; 339,98</t>
+          <t>167,17; 347,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>158,94; 348,7</t>
+          <t>157,66; 350,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 14,82</t>
+          <t>3,8; 14,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 22,61</t>
+          <t>5,35; 22,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 16,33</t>
+          <t>4,05; 16,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 9,42</t>
+          <t>-2,36; 9,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,76</t>
+          <t>5,73; 13,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 14,25</t>
+          <t>2,62; 13,08</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,31; 517,83</t>
+          <t>37,15; 505,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,55; 734,25</t>
+          <t>59,75; 764,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,07; 652,86</t>
+          <t>47,54; 644,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 404,14</t>
+          <t>-44,65; 388,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,14; 427,22</t>
+          <t>86,78; 416,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,34; 427,29</t>
+          <t>36,67; 394,91</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 12,04</t>
+          <t>4,42; 12,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,94</t>
+          <t>6,04; 17,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 14,91</t>
+          <t>6,65; 15,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 12,29</t>
+          <t>3,46; 12,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 12,44</t>
+          <t>6,72; 12,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 12,86</t>
+          <t>5,83; 13,26</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,67; 587,34</t>
+          <t>86,23; 638,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>125,34; 799,15</t>
+          <t>119,49; 837,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138,19; 701,86</t>
+          <t>115,64; 654,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,56; 548,65</t>
+          <t>61,83; 500,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>139,58; 493,92</t>
+          <t>141,64; 511,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>123,42; 488,31</t>
+          <t>123,08; 505,39</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 14,8</t>
+          <t>5,7; 15,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,07</t>
+          <t>2,99; 12,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 17,75</t>
+          <t>6,91; 17,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 20,18</t>
+          <t>7,55; 21,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 14,64</t>
+          <t>7,55; 14,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,2</t>
+          <t>6,92; 15,34</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,93; 862,35</t>
+          <t>90,54; 978,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,37; 716,14</t>
+          <t>32,01; 727,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,5; 673,26</t>
+          <t>86,47; 671,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87,54; 615,15</t>
+          <t>86,78; 725,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>124,43; 541,84</t>
+          <t>126,47; 546,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115,95; 576,16</t>
+          <t>118,25; 566,14</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,78</t>
+          <t>3,78; 13,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 15,86</t>
+          <t>2,82; 15,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 15,65</t>
+          <t>5,47; 15,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,51; 16,29</t>
+          <t>5,68; 16,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,66</t>
+          <t>6,28; 13,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,26</t>
+          <t>5,59; 14,07</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,71; 413,96</t>
+          <t>42,66; 406,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,38; 450,68</t>
+          <t>28,89; 420,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82,63; 729,96</t>
+          <t>90,23; 766,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94,0; 804,82</t>
+          <t>86,34; 761,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>106,44; 424,09</t>
+          <t>100,39; 437,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,93; 442,59</t>
+          <t>91,22; 451,88</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,6</t>
+          <t>6,72; 11,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,06</t>
+          <t>6,42; 13,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,96</t>
+          <t>8,52; 13,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,92; 13,2</t>
+          <t>6,98; 12,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,89</t>
+          <t>8,27; 11,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,17</t>
+          <t>7,47; 12,09</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>131,52; 356,52</t>
+          <t>120,54; 348,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>133,5; 387,4</t>
+          <t>126,67; 386,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168,1; 440,27</t>
+          <t>163,7; 410,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>135,43; 396,57</t>
+          <t>137,27; 390,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>167,17; 347,95</t>
+          <t>172,66; 347,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>157,66; 350,6</t>
+          <t>160,47; 351,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Edad-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,91</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>9,12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12,9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,91</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>13,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>9,02</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 14,52</t>
+          <t>4,29; 16,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 22,61</t>
+          <t>-1,37; 11,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 16,07</t>
+          <t>3,62; 14,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 9,7</t>
+          <t>5,41; 22,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,96</t>
+          <t>5,82; 13,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 13,08</t>
+          <t>4,05; 15,84</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>215,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>92,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>191,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>271,2%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>215,88%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>286,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>166,16%</t>
+          <t>192,89%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 505,66</t>
+          <t>52,0; 705,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,75; 764,9</t>
+          <t>-31,3; 463,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,54; 644,02</t>
+          <t>41,9; 583,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 388,8</t>
+          <t>75,43; 773,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,78; 416,89</t>
+          <t>87,98; 432,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,67; 394,91</t>
+          <t>53,13; 459,55</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>8,12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10,89</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,96</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>8,14</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 12,29</t>
+          <t>7,46; 15,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 17,14</t>
+          <t>3,47; 12,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 15,34</t>
+          <t>4,31; 12,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 12,16</t>
+          <t>4,91; 14,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,45</t>
+          <t>6,67; 12,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 13,26</t>
+          <t>5,28; 11,74</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>304,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>194,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>238,33%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>319,6%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>304,24%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209,3%</t>
+          <t>274,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>259,3%</t>
+          <t>231,72%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,23; 638,64</t>
+          <t>138,3; 692,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>119,49; 837,41</t>
+          <t>58,68; 509,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115,64; 654,07</t>
+          <t>65,21; 642,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,83; 500,64</t>
+          <t>97,41; 714,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>141,64; 511,71</t>
+          <t>140,55; 484,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>123,08; 505,39</t>
+          <t>108,7; 423,78</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,99</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,51</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>10,28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,55</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,99</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,31</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>9,71</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,06</t>
+          <t>6,5; 17,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,73</t>
+          <t>6,04; 18,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 17,44</t>
+          <t>5,84; 15,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 21,02</t>
+          <t>3,16; 12,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,83</t>
+          <t>7,56; 14,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 15,34</t>
+          <t>6,05; 13,73</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>241,95%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>232,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>325,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>239,06%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>241,95%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268,65%</t>
+          <t>239,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>265,62%</t>
+          <t>239,02%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,54; 978,9</t>
+          <t>77,69; 592,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,01; 727,95</t>
+          <t>71,49; 649,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,47; 671,7</t>
+          <t>97,61; 969,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86,78; 725,24</t>
+          <t>41,67; 805,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>126,47; 546,02</t>
+          <t>116,1; 540,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>118,25; 566,14</t>
+          <t>104,45; 491,76</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10,53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>8,9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8,6</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,53</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>7,17</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 13,95</t>
+          <t>5,68; 15,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,76</t>
+          <t>3,54; 12,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 15,82</t>
+          <t>4,01; 14,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 16,67</t>
+          <t>1,98; 10,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 13,39</t>
+          <t>5,9; 13,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 14,07</t>
+          <t>3,98; 10,28</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>299,24%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>227,39%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>168,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>162,67%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>299,24%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>290,56%</t>
+          <t>119,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>215,25%</t>
+          <t>163,64%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,66; 406,0</t>
+          <t>89,61; 667,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,89; 420,28</t>
+          <t>52,07; 592,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,23; 766,26</t>
+          <t>45,88; 423,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,34; 761,59</t>
+          <t>19,68; 331,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>100,39; 437,63</t>
+          <t>97,38; 413,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,22; 451,88</t>
+          <t>67,17; 348,54</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10,98</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,47</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>9,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10,98</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>8,3</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,38</t>
+          <t>8,41; 13,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,11</t>
+          <t>5,87; 11,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,47</t>
+          <t>6,94; 11,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,98; 12,95</t>
+          <t>5,62; 10,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,91</t>
+          <t>8,22; 11,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,09</t>
+          <t>6,54; 10,27</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>270,36%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>208,73%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>221,73%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>230,24%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>270,36%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241,97%</t>
+          <t>198,43%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>236,44%</t>
+          <t>203,82%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>120,54; 348,25</t>
+          <t>168,12; 436,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>126,67; 386,93</t>
+          <t>112,68; 347,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163,7; 410,62</t>
+          <t>134,44; 351,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137,27; 390,23</t>
+          <t>107,85; 332,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>172,66; 347,91</t>
+          <t>173,21; 339,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>160,47; 351,65</t>
+          <t>141,12; 298,9</t>
         </is>
       </c>
     </row>
